--- a/ClueLayout/ClueLayout.xlsx
+++ b/ClueLayout/ClueLayout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocki\Desktop\Clue Repo\ClueRepo\ClueLayout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF7F6BA7-FCDE-4432-AD88-9F14039D65D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1293615C-9B56-4551-8FA4-DDC7A3F0C5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{88D44900-2CB3-4386-A592-6E0FBA31EB14}"/>
   </bookViews>
@@ -20,22 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="38">
   <si>
     <t>W</t>
   </si>
@@ -64,9 +54,6 @@
     <t>C#</t>
   </si>
   <si>
-    <t>CS</t>
-  </si>
-  <si>
     <t>O</t>
   </si>
   <si>
@@ -130,12 +117,6 @@
     <t>B*</t>
   </si>
   <si>
-    <t>BS</t>
-  </si>
-  <si>
-    <t>PS</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -143,6 +124,21 @@
   </si>
   <si>
     <t>A*</t>
+  </si>
+  <si>
+    <t>Number of doors: 14</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>MP</t>
   </si>
 </sst>
 </file>
@@ -164,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,6 +197,42 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -214,13 +246,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,14 +573,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E9DAC4-E895-4D8B-AE27-681F795BA6E5}">
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
     <col min="2" max="22" width="3.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>0</v>
       </c>
@@ -606,19 +644,22 @@
       <c r="V1">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>32</v>
+      <c r="B2" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>0</v>
@@ -627,40 +668,40 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>0</v>
@@ -675,18 +716,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>0</v>
@@ -695,40 +736,40 @@
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>1</v>
@@ -743,60 +784,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>0</v>
@@ -811,60 +852,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>0</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="R5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>0</v>
@@ -879,18 +920,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>0</v>
@@ -902,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>0</v>
@@ -947,11 +988,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -996,7 +1037,7 @@
       <c r="P7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="10" t="s">
         <v>0</v>
       </c>
       <c r="R7" s="4" t="s">
@@ -1011,21 +1052,21 @@
       <c r="U7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="V7" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1058,7 +1099,7 @@
       <c r="N8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="8" t="s">
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
@@ -1083,21 +1124,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>0</v>
@@ -1147,28 +1188,28 @@
       <c r="U9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V9" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>0</v>
@@ -1194,13 +1235,13 @@
       <c r="N10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="s">
@@ -1219,24 +1260,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>0</v>
@@ -1274,7 +1315,7 @@
       <c r="R11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="S11" s="5" t="s">
+      <c r="S11" s="10" t="s">
         <v>4</v>
       </c>
       <c r="T11" s="4" t="s">
@@ -1287,24 +1328,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>0</v>
@@ -1340,39 +1381,39 @@
         <v>0</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>0</v>
@@ -1408,36 +1449,36 @@
         <v>0</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>0</v>
@@ -1472,39 +1513,39 @@
       <c r="P14" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="Q14" s="5" t="s">
+      <c r="Q14" s="6" t="s">
         <v>5</v>
       </c>
       <c r="R14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="U14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -1544,22 +1585,22 @@
         <v>0</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1612,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>2</v>
@@ -1700,10 +1741,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>0</v>
@@ -1717,7 +1758,7 @@
       <c r="G18" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="8" t="s">
         <v>4</v>
       </c>
       <c r="I18" s="4" t="s">
@@ -1738,7 +1779,7 @@
       <c r="N18" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="7" t="s">
         <v>0</v>
       </c>
       <c r="P18" s="4" t="s">
@@ -1768,13 +1809,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>1</v>
@@ -1783,22 +1824,22 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>0</v>
@@ -1810,25 +1851,25 @@
         <v>0</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
@@ -1836,13 +1877,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>0</v>
@@ -1851,24 +1892,24 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>1</v>
       </c>
       <c r="N20" s="4" t="s">
@@ -1878,63 +1919,63 @@
         <v>0</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>31</v>
+      <c r="B21" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>0</v>
@@ -1945,26 +1986,26 @@
       <c r="O21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="10" t="s">
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
@@ -1972,13 +2013,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>0</v>
@@ -1987,25 +2028,25 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="4" t="s">
         <v>0</v>
@@ -2017,22 +2058,22 @@
         <v>5</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
@@ -2043,37 +2084,37 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>2</v>
@@ -2085,22 +2126,22 @@
         <v>2</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
